--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0207.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0207.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Một số Nút Giấc Mơ đặc biệt có &lt;color=#ffd12f&gt;enhanced&lt;/color&gt; được tăng cường.</t>
+          <t>Một số Nút Giấc Mơ đặc biệt có &lt;color=#ffd12f&gt;Tacet Discord Ác Mộng&lt;/color&gt; được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Để hoàn thành thử thách, &lt;color=#ffd12f&gt;meet all challenge goals within the time limit&lt;/color&gt; hoặc đánh bại trực tiếp lũ Tacet Discord Ác Mộng.</t>
+          <t>Để hoàn thành thử thách, &lt;color=#ffd12f&gt;hãy đạt tất cả mục tiêu trong thời gian giới hạn&lt;/color&gt; hoặc đánh bại trực tiếp lũ Tacet Discord Ác Mộng.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Khi một quân cờ đen đặt vào vòng ngoài, nó sẽ &lt;color=#ffd12f&gt;opens all gates and maze walls in that direction.&lt;/color&gt;</t>
+          <t>Khi một quân cờ đen đặt vào vòng ngoài, nó sẽ &lt;color=#ffd12f&gt;mở tất cả các cổng và bức tường mê cung theo hướng đó.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bạn có thể tạm dừng trò chơi bất cứ lúc nào, và &lt;color=#ffd12f&gt;all pieces will stay in place.&lt;/color&gt;</t>
+          <t>Bạn có thể tạm dừng trò chơi bất cứ lúc nào, và &lt;color=#ffd12f&gt;mọi mảnh ghép sẽ giữ nguyên vị trí.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Nhấn vào nút &lt;color=#ffd12f&gt;nút Đặt lại&lt;/color&gt; để khởi động lại trò chơi.</t>
+          <t>Nhấn vào nút &lt;color=#ffd12f&gt;Reset&lt;/color&gt; để khởi động lại trò chơi.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>Trò chơi kết thúc khi quân của một bên xếp thành hàng thẳng.
-&lt;color=#ffd12f&gt;If black pieces connect, you win&lt;/color&gt;; nếu quân trắng nối liền, Lifer thắng.</t>
+&lt;color=#ffd12f&gt;Nếu quân đen nối liền, ngươi thắng&lt;/color&gt;; nếu quân trắng nối liền, Lifer thắng.</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#ffd12f&gt;Sensor&lt;/color&gt; để xác định vị trí các Thiết bị đầu cuối cấp hiệu ứng tăng cường cho Lifer.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;Cảm Biến&lt;/color&gt; để xác định vị trí các Thiết bị đầu cuối cấp hiệu ứng tăng cường cho Lifer.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nộp &lt;color=#ffd12f&gt;Stake of Imbalance&lt;/color&gt; vào Thiết bị đầu cuối để loại bỏ hiệu ứng tăng cường.</t>
+          <t>Nộp &lt;color=#ffd12f&gt;Cọc Mất Cân Bằng&lt;/color&gt; vào Thiết bị đầu cuối để loại bỏ hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sau khi nộp các Cọc, bạn có thể tự do &lt;color=#ffd12f&gt;turn The Lifer's buffs on or off&lt;/color&gt; qua Thiết bị đầu cuối.</t>
+          <t>Sau khi nộp các Cọc, bạn có thể tự do &lt;color=#ffd12f&gt;bật/tắt các hiệu ứng của The Lifer&lt;/color&gt; qua Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;When only the player is within the altar's range&lt;/color&gt;, các bia đá sẽ nạp năng lượng hiệu quả nhất.</t>
+          <t>Khi &lt;color=#ffd12f&gt;chỉ có người chơi ở trong phạm vi bàn thờ&lt;/color&gt;, các bia đá sẽ nạp năng lượng hiệu quả nhất.</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;When there are Tacet Discords within the altar's range&lt;/color&gt;, các bia đá sẽ ngừng nạp năng lượng.</t>
+          <t>Khi &lt;color=#ffd12f&gt;có Tacet Discord trong phạm vi bàn thờ&lt;/color&gt;, các bia đá sẽ ngừng nạp năng lượng.</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;When the player is out of the alter's range,&lt;/color&gt;, các bia đá sẽ ngừng nạp năng lượng và bắt đầu tiêu hao năng lượng.</t>
+          <t>Khi &lt;color=#ffd12f&gt;người chơi rời khỏi phạm vi bàn thờ&lt;/color&gt;, các bia đá sẽ ngừng nạp năng lượng và bắt đầu tiêu hao năng lượng.</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>{0} Dùng đèn để di chuyển giữa các chiều không gian.</t>
+          <t>Dùng đèn để di chuyển giữa các chiều không gian.</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>{0} Nhấn để sử dụng Thiết Bị Dọn Dẹp.</t>
+          <t>Nhấn để sử dụng Thiết Bị Dọn Dẹp.</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; và chuyển đổi &lt;color=#ffd12f&gt;Attribute&lt;/color&gt; của Rover</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; và chuyển đổi &lt;color=#ffd12f&gt;Thuộc Tính&lt;/color&gt; của Rover</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; và chuyển đổi &lt;color=#ffd12f&gt;Attribute&lt;/color&gt; của Rover</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; và chuyển đổi &lt;color=#ffd12f&gt;Thuộc Tính&lt;/color&gt; của Rover</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể gọi Phaom để di chuyển.</t>
+          <t>{0} Giờ cậu có thể gọi Phaom để di chuyển rồi.</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Dây leo chặn đường tiến của Phaom. Hãy tìm và dùng &lt;color=#ffd12f&gt;Remnant Sparks&lt;/color&gt; để khai thông lối đi!</t>
+          <t>Dây leo chặn đường tiến của Phaom. Hãy tìm và dùng &lt;color=#ffd12f&gt;Tàn Lửa Dư Hồng&lt;/color&gt; để khai thông lối đi!</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Ném &lt;color=#ffd12f&gt;Throw the Remnant Spark&lt;/color&gt; vào dây leo để thanh tẩy chúng.</t>
+          <t>Ném &lt;color=#ffd12f&gt;Tàn Dư Lửa&lt;/color&gt; vào dây leo để thanh tẩy chúng.</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=#ffd12f&gt;Whistle from Công cụ&lt;/color&gt; gần vùng nước có trọng lực phù hợp để triệu hồi Phaom, bạn đồng hành của Cartethyia, để cưỡi.</t>
+          <t>Sử dụng &lt;color=#ffd12f&gt;Huýt Sáo từ Công Cụ&lt;/color&gt; gần vùng nước có trọng lực phù hợp để triệu hồi Phaom, bạn đồng hành của Cartethyia, để cưỡi.</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Một số bức tranh Palette Tràn đầy chứa các Khối Màu được hình thành từ tần số bất thường. &lt;color=#ffd12f&gt;These blocks cannot be colored normally&lt;/color&gt; được.</t>
+          <t>Một số bức tranh Palette Tràn đầy chứa các Khối Màu được hình thành từ tần số bất thường. &lt;color=#ffd12f&gt;Những khối này không thể tô màu bình thường&lt;/color&gt; được.</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Khả năng của một số Cộng Hưởng Giả bị hạn chế trong môi trường trọng lực nhất định.</t>
+          <t>Khả năng của một số Resonator bị hạn chế trong môi trường trọng lực nhất định.</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Nhờ khả năng điều khiển thuyền siêu đỉnh của Phaom, cậu có thể lướt lên thác nước để đến &lt;color=#ffd12f&gt;areas with different gravity orientations&lt;/color&gt;.</t>
+          <t>Nhờ khả năng điều khiển thuyền siêu đỉnh của Phaom, cậu có thể lướt lên thác nước để đến &lt;color=#ffd12f&gt;những khu vực có hướng trọng lực khác nhau&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>&lt;alignleft/&gt;Sau khi kích hoạt, hiệu ứng Khía Cạnh Bay/Lượn sẽ áp dụng cho tất cả Cộng Hưởng Giả hiện tại. Các Cộng Hưởng Giả nhận được sau này sẽ không bị ảnh hưởng.</t>
+          <t>&lt;alignleft/&gt;Sau khi kích hoạt, hiệu ứng Khía Cạnh Bay/Lượn sẽ áp dụng cho tất cả Resonator hiện tại. Các Resonator nhận được sau này sẽ không bị ảnh hưởng.</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Liên tục tấn công &lt;color=#8c7e51&gt;Sequence Mechanism&lt;/color&gt; để kích hoạt và mở công tắc tương ứng.</t>
+          <t>Liên tục tấn công &lt;color=#8c7e51&gt;Cơ Chế Trình Tự&lt;/color&gt; để kích hoạt và mở công tắc tương ứng.</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Liên tục tấn công &lt;color=#8c7e51&gt;Sequence Mechanism&lt;/color&gt; để kích hoạt và mở công tắc tương ứng.</t>
+          <t>Liên tục tấn công &lt;color=#8c7e51&gt;Cơ Chế Trình Tự&lt;/color&gt; để kích hoạt và mở công tắc tương ứng.</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Liên tục tấn công &lt;color=#8c7e51&gt;Sequence Mechanism&lt;/color&gt; để kích hoạt và mở công tắc tương ứng.</t>
+          <t>Liên tục tấn công &lt;color=#8c7e51&gt;Cơ Chế Trình Tự&lt;/color&gt; để kích hoạt và mở công tắc tương ứng.</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Trong mỗi vòng đua, bạn sẽ gặp các Cube Cộng Hưởng Giả. Hãy gặp họ để kích hoạt phần thưởng đặc biệt của Cube!</t>
+          <t>Trong mỗi vòng đua, bạn sẽ gặp các Cube Resonator. Hãy gặp họ để kích hoạt phần thưởng đặc biệt của Cube!</t>
         </is>
       </c>
     </row>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Các Mô-đun Dữ Liệu Phụ có thể được &lt;color=#ffd12f&gt;decompiled&lt;/color&gt; và tái chế thành vật liệu nâng cấp.</t>
+          <t>Các Mô-đun Dữ Liệu Phụ có thể được &lt;color=#ffd12f&gt;giải mã&lt;/color&gt; và tái chế thành vật liệu nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Tăng cấp Khối Lập Phương sẽ &lt;color=#ffd12f&gt;unlocks&lt;/color&gt; thêm &lt;color=#ffd12f&gt;slots&lt;/color&gt; trong Mô-đun Dữ liệu, cho phép gắn thêm nhiều Mô-đun Dữ liệu hơn.</t>
+          <t>Tăng cấp Khối Lập Phương sẽ &lt;color=#ffd12f&gt;mở khóa&lt;/color&gt; thêm &lt;color=#ffd12f&gt;ô dữ liệu&lt;/color&gt; trong Mô-đun Dữ liệu, cho phép gắn thêm nhiều Mô-đun Dữ liệu hơn.</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Tên của Rover sẽ hiển thị phía trên mô hình Cộng Hưởng Giả trong Chế Độ Hợp Tác.</t>
+          <t>Tên của Vận Mệnh Giả sẽ hiển thị phía trên mô hình Resonator trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{0} Dùng Orchestration để thay đổi trạng thái của các vật thể gần đó.</t>
+          <t>Sử dụng Orchestration để thay đổi trạng thái của các vật thể gần đó.</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=press Gamepad=press} để quỳ một gối cầu nguyện.</t>
+          <t>Nhấn {0} để quỳ một gối cầu nguyện</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=press Gamepad=press} để chắp tay cầu nguyện.</t>
+          <t>Nhấn {0} để chắp tay cầu nguyện</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=press Gamepad=press} để giơ tay cầu nguyện.</t>
+          <t>Nhấn {0} {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để giơ tay cầu nguyện.</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng.</t>
+          <t>Nếu có nhiều nốt nhạc, hãy nối tất cả các nốt đến số 5 theo màu tương ứng của chúng.</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Ngắm vào Chiến Dịch Cơ đã triển khai và dùng {0} để &lt;color=#ffd12f&gt;Recall&lt;/color&gt;. 
+          <t>Ngắm vào Chiến Dịch Cơ đã triển khai và dùng {0} để &lt;color=#ffd12f&gt;Thu Hồi&lt;/color&gt;. 
 Bạn sẽ được hoàn lại toàn bộ Sim Credits đã sử dụng.</t>
         </is>
       </c>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Ngắm vào Chiến Dịch Cơ đã triển khai và dùng {0} để &lt;color=#ffd12f&gt;Recall&lt;/color&gt;. 
+          <t>Ngắm vào Chiến Dịch Cơ đã triển khai và dùng {0} để &lt;color=#ffd12f&gt;Thu Hồi&lt;/color&gt;. 
 Bạn sẽ được hoàn lại toàn bộ Sim Credits đã sử dụng.</t>
         </is>
       </c>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Ngắm vào Chiến Dịch Cơ đã triển khai và dùng {0} để &lt;color=#ffd12f&gt;Recall&lt;/color&gt;. 
+          <t>Ngắm vào Chiến Dịch Cơ đã triển khai và dùng {0} để &lt;color=#ffd12f&gt;Thu Hồi&lt;/color&gt;. 
 Bạn sẽ được hoàn lại toàn bộ Sim Credits đã sử dụng.</t>
         </is>
       </c>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Những "đốm sáng" di chuyển sẽ đánh thức những &lt;color=#ffd12f&gt;Hollow Figures&lt;/color&gt; đang ngủ dọc đường. Hãy cẩn thận.</t>
+          <t>Những "đốm sáng" di chuyển sẽ đánh thức những &lt;color=#ffd12f&gt;Hình Nhân Rỗng&lt;/color&gt; đang ngủ dọc đường. Hãy cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Cậu có thể sử dụng vật phẩm đã mua bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} các nút tương ứng. Vật phẩm tiêu hao sẽ hết sau khi dùng.</t>
+          <t>Cậu có thể sử dụng vật phẩm đã mua bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} các nút tương ứng. Vật phẩm tiêu hao sẽ hết sau khi dùng.</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{0} Dùng Công Cụ: Bay Lượn để nhảy lên không và bắt đầu bay.</t>
+          <t>Sử dụng Utility: Flight để nhảy lên không và bắt đầu bay.</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Bay vào Đường Gió để &lt;color=#ffd12f&gt;automatically&lt;/color&gt; di chuyển theo quỹ đạo.</t>
+          <t>Bay vào Đường Gió để &lt;color=#ffd12f&gt;tự động&lt;/color&gt; di chuyển theo quỹ đạo.</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Bay vào Đường Gió để &lt;color=#ffd12f&gt;automatically&lt;/color&gt; di chuyển theo quỹ đạo.</t>
+          <t>Bay vào Đường Gió để &lt;color=#ffd12f&gt;tự động&lt;/color&gt; di chuyển theo quỹ đạo.</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Bay vào Đường Gió để &lt;color=#ffd12f&gt;automatically&lt;/color&gt; di chuyển theo quỹ đạo.</t>
+          <t>Bay vào Đường Gió để &lt;color=#ffd12f&gt;tự động&lt;/color&gt; di chuyển theo quỹ đạo.</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       <c r="M152" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Trang này giới thiệu những cập nhật quan trọng trong bản vá mới để các Rover nắm bắt những gì sắp tới.</t>
+Trang này giới thiệu những cập nhật quan trọng trong bản vá mới để các Vận Mệnh Giả nắm bắt những gì sắp tới.</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{0} Dùng "Đèn Lồng Napoli Thứ Hai" để phân tách và thay đổi thế giới trong Dark Tide</t>
+          <t>Dùng "Lantern of Napoli the Second" để phân tách và thay đổi các thế giới trong Dark Tide.</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả có thể sử dụng {0} Kỹ Năng Chủ Động và {1} Tấn Công Nhanh.</t>
+          <t>Resonator có thể sử dụng {0} Kỹ Năng Chủ Động và {1} Tấn Công Nhanh.</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả có thể sử dụng {0} Kỹ Năng Chủ Động và {1} Tấn Công Nhanh.</t>
+          <t>Resonator có thể sử dụng {0} Kỹ Năng Chủ Động và {1} Tấn Công Nhanh.</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Trong buổi diễn tập, Vũ Khí của Cộng Hưởng Giả sẽ tự động tấn công. Họ không thể sử dụng kỹ năng thông thường, nhưng có thể Lao Vút, Chạy Nhanh và sử dụng Kỹ Năng Chủ Động.</t>
+          <t>Trong buổi diễn tập, Vũ Khí của Resonator sẽ tự động tấn công. Họ không thể sử dụng kỹ năng thông thường, nhưng có thể Lao Vút, Chạy Nhanh và sử dụng Kỹ Năng Chủ Động.</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Vũ khí mới mở khóa ở các đợt sóng nhất định. Cộng Hưởng Giả sẽ sử dụng nhiều vũ khí cùng lúc.</t>
+          <t>Vũ khí mới mở khóa ở các đợt sóng nhất định. Resonator sẽ sử dụng nhiều vũ khí cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Mỗi Thử Thách Chụp Ảnh Đóng Băng sẽ đưa ra ba mục tiêu chụp ảnh. Hoàn thành chúng bằng cách chụp Cộng Hưởng Giả thực hiện các hành động chiến đấu yêu cầu.</t>
+          <t>Mỗi Thử Thách Chụp Ảnh Đóng Băng sẽ đưa ra ba mục tiêu chụp ảnh. Hoàn thành chúng bằng cách chụp Resonator thực hiện các hành động chiến đấu yêu cầu.</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Sticker chứa Năng Lượng Tàn Dư có thể khai thác. Những Sticker này có thể được trang bị trong giao diện Túi Lưu Trữ để mang lại nhiều loại tăng cường cho Cộng Hưởng Giả.</t>
+          <t>Sticker chứa Năng Lượng Tàn Dư có thể khai thác. Những Sticker này có thể được trang bị trong giao diện Túi Lưu Trữ để mang lại nhiều loại tăng cường cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Khi khám phá Honami City, Lament Residue sẽ dần dần làm tha hóa Cộng Hưởng Giả của cậu. Khả năng chống lại sự tha hóa này được thể hiện qua chỉ số Stability.</t>
+          <t>Khi khám phá Honami City, Lament Residue sẽ dần dần làm tha hóa Resonator của cậu. Khả năng chống lại sự tha hóa này được thể hiện qua chỉ số Stability.</t>
         </is>
       </c>
     </row>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} để triệu hồi xe máy.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để triệu hồi xe máy.</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Giữ {0}/{1} và nhấn {2} để trượt drift</t>
+          <t>Giữ {1}/{0} và nhấn {2} để trượt drift</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12889,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}/{1} để Bounce Nhảy</t>
+          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} {0}/{1} để Bounce Jump</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để Bounce Nhảy</t>
+          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} {0} để Bounce Jump</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Attack Xuống Thú</t>
+          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Đòn Hạ Thú</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Attack Xuống Thú</t>
+          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Đòn Hạ Thú</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}/{1} để Bounce Nhảy</t>
+          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} {0}/{1} để Bounce Jump</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để Bounce Nhảy</t>
+          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} {0} để Bounce Jump</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tránh chướng ngại vật bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để Bật Nhảy</t>
+          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} Nhảy để Bật Nhảy</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Giữ {0} trong Chế Độ Điện Ảnh để mời Cộng Hưởng Giả tham gia Đi Chung</t>
+          <t>Giữ {0} trong Chế Độ Điện Ảnh để mời Resonator tham gia Đi Chung</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Giữ {0} trong Chế Độ Điện Ảnh để mời Cộng Hưởng Giả tham gia Đi Chung</t>
+          <t>Giữ {0} trong Chế Độ Điện Ảnh để mời Resonator tham gia Đi Chung</t>
         </is>
       </c>
     </row>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển Tune Break.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để thi triển Tune Break.</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển Tune Break.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để thi triển Tune Break.</t>
         </is>
       </c>
     </row>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển Tune Break.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để thi triển Tune Break.</t>
         </is>
       </c>
     </row>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển Tune Break.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để thi triển Tune Break.</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>{0} Dùng Projector để tạo Echo Projection cho các tương tác đặc biệt</t>
+          <t>Sử dụng Projector để tạo Echo Projection cho các tương tác đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tương Tác để Di Chuyển Nhanh đến Điểm Đến.</t>
+          <t>Tương Tác để dịch Chuyển Nhanh đến Điểm Đến.</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Vài con Soliskin lạc đường qua tận Lahai-Roi. Tìm và dẫn chúng về lại Rừng Bjartr đi.</t>
+          <t>Vài con Soliskin lạc đường qua tận Lahai-Roi. Tìm và dẫn chúng về lại Bjartr Woods đi.</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Khi đến gần ray, {Cus:Ipt,Touch=tap PC=ấn Gamepad=ấn} nút Nhảy để bắt đầu Trượt Ray.</t>
+          <t>Khi đến gần ray, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Nhảy để bắt đầu Trượt Ray.</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Điều khiển xe máy thám hiểm, vượt qua các Vòng Điểm để &lt;color=#ffd12f&gt;collect points&lt;/color&gt; trong khi tiến về đích.</t>
+          <t>Điều khiển xe máy thám hiểm, vượt qua các Vòng Điểm để &lt;color=#ffd12f&gt;thu thập điểm&lt;/color&gt; trong khi tiến về đích.</t>
         </is>
       </c>
     </row>
@@ -16204,7 +16204,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Giữ {0}/{1} và dùng {2} để nhảy khỏi ray</t>
+          <t>Giữ {1}/{0} và dùng {2} để nhảy khỏi ray</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Sau khi trang trí xong, {Cus:Ipt,Touch=tap PC=click Gamepad=press} Lưu Thiết Kế để lưu lại các vật trang trí &lt;color=#ffd12f&gt;in this area&lt;/color&gt;.</t>
+          <t>Sau khi trang trí xong, {Cus:Ipt,Touch=tap PC=click Gamepad=press} Lưu Thiết Kế để lưu lại các vật trang trí &lt;color=#ffd12f&gt;trong khu vực này&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Dùng Bộ Chuyển Đổi Mô-đun bắn vào các Nhân Tần Số Bất Ổn, chuyển đổi chúng giữa trạng thái vật chất và phi vật chất.</t>
+          <t>Dùng Bộ Chuyển Đổi Module bắn vào các Nhân Tần Số Bất Ổn, chuyển đổi chúng giữa trạng thái vật chất và phi vật chất.</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Di chuyển Cộng Hưởng Giả sang trái hoặc phải để thu thập thức ăn và kiếm Điểm Ẩm Thực.</t>
+          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm Điểm Ẩm Thực.</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>{0} Dùng Rune: Nhấn Switch để thay đổi trạng thái Switchgate trong môi trường này</t>
+          <t>Dùng Rune: Switch để thay đổi trạng thái của Switchgate trong môi trường này.</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Bộ trống được cất giấu ngẫu nhiên ở Dark Side. Khi Cộng Hưởng Giả dẫm lên, chũm chọe sẽ nghiêng sang một bên.</t>
+          <t>Bộ trống được cất giấu ngẫu nhiên ở Dark Side. Khi Resonator dẫm lên, chũm chọe sẽ nghiêng sang một bên.</t>
         </is>
       </c>
     </row>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>{0} Dùng bùa Sigrika đã khắc cho bạn để cảm nhận mảnh vỡ bùa Royan gần đó.</t>
+          <t>Dùng ký tự Sigrika đã được khắc cho ngươi để cảm nhận những mảnh vỡ ký tự Royan gần đây.</t>
         </is>
       </c>
     </row>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Luồng đua thay đổi theo từng giai đoạn, và thứ hạng trận đấu quyết định liệu Khối Lập Phương có &lt;color=#ffd12f&gt;advances&lt;/color&gt; vòng tiếp theo hay không.</t>
+          <t>Luồng đua thay đổi theo từng giai đoạn, và thứ hạng trận đấu quyết định liệu Khối Lập Phương có &lt;color=#ffd12f&gt;tiến vào&lt;/color&gt; vòng tiếp theo hay không.</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Triệu hồi Spacetrek Explorer để tạo Khiên cho Cộng Hưởng Giả.</t>
+          <t>Triệu hồi Spacetrek Explorer để tạo Khiên cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -22986,7 +22986,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Triệu hồi Hồn Mây Nimbus để hồi phục HP cho Cộng Hưởng Giả đang hoạt động.</t>
+          <t>Triệu hồi Hồn Mây Nimbus để hồi phục HP cho Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -23116,7 +23116,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Triệu hồi một Calcified Junrock để chữa trị cho các Cộng Hưởng Giả gần đó trong đội.</t>
+          <t>Triệu hồi một Calcified Junrock để chữa trị cho các Resonator gần đó trong đội.</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23246,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Mid-air Attack - Ashfall Barrage&lt;/color&gt;: Khi ở trên không, giữ {0}.</t>
+          <t>&lt;color=Highlight&gt;Tấn Công Giữa Không - Ashfall Barrage&lt;/color&gt;: Khi ở trên không, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -23311,7 +23311,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Hellstride&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} trong khi thực hiện hành động chiến đấu.</t>
+          <t>&lt;color=Highlight&gt;Hellstride&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} trong khi thực hiện hành động chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Vụ Nổ Sắc Cầu: {Cus:Ipt,Touch=tap PC=press Gamepad=press}</t>
+          <t>Vụ Nổ Sắc Cầu: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press}</t>
         </is>
       </c>
     </row>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Bản Duet Thần Thánh: khi &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; đạt 50%, {0}+{0}+{0}+{0}+{1}.</t>
+          <t>Bản Duet Thần Thánh: khi &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt; đạt 50%, {0}+{0}+{0}+{0}+{1}.</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Sơ Đồ Rune: Giữ {0} với 2 &lt;color=Highlight&gt;Runes&lt;/color&gt;</t>
+          <t>Sơ Đồ Rune: Giữ {0} với 2 &lt;color=Highlight&gt;Rune&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24026,7 +24026,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Học Tên Thật Của Ta: Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đạt tối đa, giữ {0}</t>
+          <t>Học Tên Thật Của Ta: Khi &lt;color=Highlight&gt;Dừng Hoàn Toàn&lt;/color&gt; đạt tối đa, giữ {0}</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=Highlight&gt;Cosmic Beat&lt;/color&gt; để biểu diễn &lt;color=Highlight&gt;Solo Concert&lt;/color&gt;: Khi đang ở trên không, {0}+{0}+{0}.</t>
+          <t>Sử dụng &lt;color=Highlight&gt;Nhịp Vũ Trụ&lt;/color&gt; để biểu diễn &lt;color=Highlight&gt;Độc Tấu Hoàn Mỹ&lt;/color&gt;: Khi đang ở trên không, {0}+{0}+{0}.</t>
         </is>
       </c>
     </row>
@@ -27016,7 +27016,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Khởi đầu của hành trình chinh phục đỉnh cao. Một lưỡi kiếm rộng được chế tác cho những Cộng Hưởng Giả mới. Đừng đánh giá thấp sức mạnh ẩn giấu dưới vẻ ngoài đơn giản của nó.</t>
+          <t>Khởi đầu của hành trình chinh phục đỉnh cao. Một lưỡi kiếm rộng được chế tác cho những Resonator mới. Đừng đánh giá thấp sức mạnh ẩn giấu dưới vẻ ngoài đơn giản của nó.</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Khởi đầu của hành trình chinh phục đỉnh cao. Một lưỡi kiếm rộng được chế tác cho những Cộng Hưởng Giả mới. Đừng đánh giá thấp sức mạnh ẩn giấu dưới vẻ ngoài đơn giản của nó.</t>
+          <t>Khởi đầu của hành trình chinh phục đỉnh cao. Một lưỡi kiếm rộng được chế tác cho những Resonator mới. Đừng đánh giá thấp sức mạnh ẩn giấu dưới vẻ ngoài đơn giản của nó.</t>
         </is>
       </c>
     </row>
@@ -27146,7 +27146,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Khởi đầu của hành trình chinh phục đỉnh cao. Một lưỡi kiếm rộng được chế tác cho những Cộng Hưởng Giả mới. Đừng đánh giá thấp sức mạnh ẩn giấu dưới vẻ ngoài đơn giản của nó.</t>
+          <t>Khởi đầu của hành trình chinh phục đỉnh cao. Một lưỡi kiếm rộng được chế tác cho những Resonator mới. Đừng đánh giá thấp sức mạnh ẩn giấu dưới vẻ ngoài đơn giản của nó.</t>
         </is>
       </c>
     </row>
@@ -30286,7 +30286,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Sự ra đời của những đợt thủy triều cách mạng. Một thanh kiếm được chế tác cho Cộng Hưởng Giả mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Sự ra đời của những đợt thủy triều cách mạng. Một thanh kiếm được chế tác cho Resonator mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -30351,7 +30351,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Sự ra đời của những đợt thủy triều cách mạng. Một thanh kiếm được chế tác cho Cộng Hưởng Giả mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Sự ra đời của những đợt thủy triều cách mạng. Một thanh kiếm được chế tác cho Resonator mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -30416,7 +30416,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Sự ra đời của những đợt thủy triều cách mạng. Một thanh kiếm được chế tác cho Cộng Hưởng Giả mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Sự ra đời của những đợt thủy triều cách mạng. Một thanh kiếm được chế tác cho Resonator mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -31651,7 +31651,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Khởi đầu của cuộc phiêu lưu dũng cảm. Một cặp súng lục được thiết kế cho Cộng Hưởng Giả mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Khởi đầu của cuộc phiêu lưu dũng cảm. Một cặp súng lục được thiết kế cho Resonator mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Khởi đầu của cuộc phiêu lưu dũng cảm. Một cặp súng lục được thiết kế cho Cộng Hưởng Giả mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Khởi đầu của cuộc phiêu lưu dũng cảm. Một cặp súng lục được thiết kế cho Resonator mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -31781,7 +31781,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khởi đầu của cuộc phiêu lưu dũng cảm. Một cặp súng lục được thiết kế cho Cộng Hưởng Giả mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Khởi đầu của cuộc phiêu lưu dũng cảm. Một cặp súng lục được thiết kế cho Resonator mới vào nghề. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -33016,7 +33016,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Bình minh của nỗ lực bền bỉ. Một đôi găng tay được chế tạo dành cho Cộng Hưởng Giả mới. Ẩn chứa bên trong vẻ ngoài giản đơn là một sức mạnh không thể xem thường.</t>
+          <t>Bình minh của nỗ lực bền bỉ. Một đôi găng tay được chế tạo dành cho Resonator mới. Ẩn chứa bên trong vẻ ngoài giản đơn là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -33081,7 +33081,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Bình minh của nỗ lực bền bỉ. Một đôi găng tay được chế tạo dành cho Cộng Hưởng Giả mới. Ẩn chứa bên trong vẻ ngoài giản đơn là một sức mạnh không thể xem thường.</t>
+          <t>Bình minh của nỗ lực bền bỉ. Một đôi găng tay được chế tạo dành cho Resonator mới. Ẩn chứa bên trong vẻ ngoài giản đơn là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
